--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A5B3423-6DE4-B644-9C1B-3A7631E1EEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA831B-AC9C-2A43-9A2C-6921913A1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3820" yWindow="2400" windowWidth="28040" windowHeight="17180" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
+    <workbookView xWindow="5620" yWindow="2160" windowWidth="28040" windowHeight="17180" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -236,9 +236,6 @@
     <t>Diego Machado</t>
   </si>
   <si>
-    <t>Participante 24</t>
-  </si>
-  <si>
     <t>Participante 25</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>José Luis Zavala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carmen Falcones </t>
   </si>
 </sst>
 </file>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -872,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
@@ -894,7 +894,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -905,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -927,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
@@ -938,7 +938,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -960,7 +960,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
@@ -971,7 +971,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -982,7 +982,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>17</v>
@@ -993,7 +993,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
@@ -1004,7 +1004,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -1015,7 +1015,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>20</v>
@@ -1026,7 +1026,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -1037,7 +1037,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>22</v>
@@ -1048,7 +1048,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>23</v>
@@ -1059,7 +1059,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
@@ -1070,7 +1070,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -1081,7 +1081,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>26</v>
@@ -1092,7 +1092,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>27</v>
@@ -1103,7 +1103,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>28</v>
@@ -1114,7 +1114,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>29</v>
@@ -1125,7 +1125,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>30</v>
@@ -1136,7 +1136,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>31</v>
@@ -1147,7 +1147,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>32</v>
@@ -1158,7 +1158,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>33</v>
@@ -1169,7 +1169,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
@@ -1180,7 +1180,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>35</v>
@@ -1191,7 +1191,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>36</v>
@@ -1202,7 +1202,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
@@ -1213,7 +1213,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>38</v>
@@ -1224,7 +1224,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>39</v>
@@ -1235,7 +1235,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>40</v>
@@ -1246,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>41</v>
@@ -1257,7 +1257,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>42</v>
@@ -1268,7 +1268,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>43</v>
@@ -1279,7 +1279,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>44</v>
@@ -1290,7 +1290,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>45</v>
@@ -1301,7 +1301,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>46</v>
@@ -1312,7 +1312,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>47</v>
@@ -1323,7 +1323,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>48</v>
@@ -1334,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>49</v>
@@ -1345,7 +1345,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>50</v>
@@ -1356,7 +1356,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>51</v>
@@ -1367,7 +1367,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>52</v>
@@ -1378,7 +1378,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>53</v>
@@ -1389,7 +1389,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>54</v>
@@ -1400,7 +1400,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>55</v>
@@ -1411,7 +1411,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>56</v>
@@ -1422,7 +1422,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>57</v>
@@ -1433,7 +1433,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>58</v>
@@ -1444,7 +1444,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>59</v>
@@ -1455,7 +1455,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>60</v>
@@ -1466,7 +1466,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>61</v>
@@ -1477,7 +1477,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>62</v>

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA831B-AC9C-2A43-9A2C-6921913A1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5620" yWindow="2160" windowWidth="28040" windowHeight="17180" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
+    <workbookView xWindow="-24920" yWindow="3220" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA831B-AC9C-2A43-9A2C-6921913A1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF642071-09B4-E943-8EAA-43B95AE2BFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24920" yWindow="3220" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
+    <workbookView xWindow="-28800" yWindow="2560" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -236,24 +236,6 @@
     <t>Diego Machado</t>
   </si>
   <si>
-    <t>Participante 25</t>
-  </si>
-  <si>
-    <t>Participante 26</t>
-  </si>
-  <si>
-    <t>Participante 27</t>
-  </si>
-  <si>
-    <t>Participante 28</t>
-  </si>
-  <si>
-    <t>Participante 29</t>
-  </si>
-  <si>
-    <t>Participante 30</t>
-  </si>
-  <si>
     <t>Participante 31</t>
   </si>
   <si>
@@ -335,12 +317,6 @@
     <t>Gabriel Larco</t>
   </si>
   <si>
-    <t>Daniel Isaías Guevara Moreano</t>
-  </si>
-  <si>
-    <t>Christian Eduardo Guevara Vega</t>
-  </si>
-  <si>
     <t>Gabriel Cepeda</t>
   </si>
   <si>
@@ -362,15 +338,9 @@
     <t>Cristina Torres</t>
   </si>
   <si>
-    <t>Eduardo Mauricio Vásquez</t>
-  </si>
-  <si>
     <t>Nicolás Vásquez</t>
   </si>
   <si>
-    <t>Eduardo José Vásquez</t>
-  </si>
-  <si>
     <t>Roberto Mucarsel H</t>
   </si>
   <si>
@@ -405,6 +375,36 @@
   </si>
   <si>
     <t xml:space="preserve">Carmen Falcones </t>
+  </si>
+  <si>
+    <t>Margoth Jacobowitz</t>
+  </si>
+  <si>
+    <t>Antonio Torres</t>
+  </si>
+  <si>
+    <t>Bryan Montalvo</t>
+  </si>
+  <si>
+    <t>Irene Vásquez</t>
+  </si>
+  <si>
+    <t>Javier Gracia</t>
+  </si>
+  <si>
+    <t>Pepe Vaca</t>
+  </si>
+  <si>
+    <t>Eduardo M Vásquez</t>
+  </si>
+  <si>
+    <t>Eduardo J Vásquez</t>
+  </si>
+  <si>
+    <t>Daniel Guevara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian  Guevara </t>
   </si>
 </sst>
 </file>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -872,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
@@ -894,7 +894,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -905,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -927,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
@@ -938,7 +938,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -960,7 +960,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
@@ -971,7 +971,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -982,7 +982,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>17</v>
@@ -993,7 +993,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
@@ -1004,7 +1004,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -1015,7 +1015,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>20</v>
@@ -1026,7 +1026,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -1037,7 +1037,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>22</v>
@@ -1048,7 +1048,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>23</v>
@@ -1059,7 +1059,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
@@ -1070,7 +1070,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -1081,7 +1081,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>26</v>
@@ -1092,7 +1092,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>27</v>
@@ -1103,7 +1103,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>28</v>
@@ -1114,7 +1114,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>29</v>
@@ -1125,7 +1125,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>30</v>
@@ -1136,7 +1136,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>31</v>
@@ -1147,7 +1147,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>32</v>
@@ -1158,7 +1158,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>33</v>
@@ -1169,7 +1169,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
@@ -1180,7 +1180,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>35</v>
@@ -1191,7 +1191,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>36</v>
@@ -1202,7 +1202,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
@@ -1213,7 +1213,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>38</v>
@@ -1224,7 +1224,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>39</v>
@@ -1235,7 +1235,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>40</v>
@@ -1246,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>41</v>
@@ -1257,7 +1257,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>42</v>
@@ -1268,7 +1268,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>43</v>
@@ -1279,7 +1279,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>44</v>
@@ -1290,7 +1290,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>45</v>
@@ -1301,7 +1301,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>46</v>
@@ -1312,7 +1312,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>47</v>
@@ -1323,7 +1323,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>48</v>
@@ -1334,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>49</v>
@@ -1345,7 +1345,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>50</v>
@@ -1356,7 +1356,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>51</v>
@@ -1367,7 +1367,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>52</v>
@@ -1378,7 +1378,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>53</v>
@@ -1389,7 +1389,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>54</v>
@@ -1400,7 +1400,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>55</v>
@@ -1411,7 +1411,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>56</v>
@@ -1422,7 +1422,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>57</v>
@@ -1433,7 +1433,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>58</v>
@@ -1444,7 +1444,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>59</v>
@@ -1455,7 +1455,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>60</v>
@@ -1466,7 +1466,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>61</v>
@@ -1477,7 +1477,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>62</v>

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF642071-09B4-E943-8EAA-43B95AE2BFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B258C627-4CCE-BC4C-B8FF-1EB0AC41B76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="2560" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>ID</t>
   </si>
@@ -236,84 +236,6 @@
     <t>Diego Machado</t>
   </si>
   <si>
-    <t>Participante 31</t>
-  </si>
-  <si>
-    <t>Participante 32</t>
-  </si>
-  <si>
-    <t>Participante 33</t>
-  </si>
-  <si>
-    <t>Participante 34</t>
-  </si>
-  <si>
-    <t>Participante 35</t>
-  </si>
-  <si>
-    <t>Participante 36</t>
-  </si>
-  <si>
-    <t>Participante 37</t>
-  </si>
-  <si>
-    <t>Participante 38</t>
-  </si>
-  <si>
-    <t>Participante 39</t>
-  </si>
-  <si>
-    <t>Participante 40</t>
-  </si>
-  <si>
-    <t>Participante 41</t>
-  </si>
-  <si>
-    <t>Participante 42</t>
-  </si>
-  <si>
-    <t>Participante 43</t>
-  </si>
-  <si>
-    <t>Participante 44</t>
-  </si>
-  <si>
-    <t>Participante 45</t>
-  </si>
-  <si>
-    <t>Participante 46</t>
-  </si>
-  <si>
-    <t>Participante 47</t>
-  </si>
-  <si>
-    <t>Participante 48</t>
-  </si>
-  <si>
-    <t>Participante 49</t>
-  </si>
-  <si>
-    <t>Participante 50</t>
-  </si>
-  <si>
-    <t>Participante 51</t>
-  </si>
-  <si>
-    <t>Participante 52</t>
-  </si>
-  <si>
-    <t>Participante 53</t>
-  </si>
-  <si>
-    <t>Participante 54</t>
-  </si>
-  <si>
-    <t>Participante 55</t>
-  </si>
-  <si>
-    <t>Participante 56</t>
-  </si>
-  <si>
     <t>Gabriel Larco</t>
   </si>
   <si>
@@ -405,6 +327,90 @@
   </si>
   <si>
     <t xml:space="preserve">Christian  Guevara </t>
+  </si>
+  <si>
+    <t>Sergio Montalvo</t>
+  </si>
+  <si>
+    <t>Abraham Loja</t>
+  </si>
+  <si>
+    <t>Gonzalo Vásquez</t>
+  </si>
+  <si>
+    <t>Edgar Moreno</t>
+  </si>
+  <si>
+    <t>Alex Moreno</t>
+  </si>
+  <si>
+    <t>Luis Moreno</t>
+  </si>
+  <si>
+    <t>Jose Viera</t>
+  </si>
+  <si>
+    <t>Paco Ortiz</t>
+  </si>
+  <si>
+    <t>Ma José Sánchez</t>
+  </si>
+  <si>
+    <t>Andrés Ávalos</t>
+  </si>
+  <si>
+    <t>Carlos Castro</t>
+  </si>
+  <si>
+    <t>Carlitos y Patty</t>
+  </si>
+  <si>
+    <t>Doménica Larrea</t>
+  </si>
+  <si>
+    <t>Mario Viera C</t>
+  </si>
+  <si>
+    <t>Katty Naranjo</t>
+  </si>
+  <si>
+    <t>Paz Haro</t>
+  </si>
+  <si>
+    <t>Jonathan Loor</t>
+  </si>
+  <si>
+    <t>Jaime Brito</t>
+  </si>
+  <si>
+    <t>Robert Jiménez</t>
+  </si>
+  <si>
+    <t>Johnny Guevara</t>
+  </si>
+  <si>
+    <t>Martín Buitrón</t>
+  </si>
+  <si>
+    <t>Antony Ramos</t>
+  </si>
+  <si>
+    <t>Edison Orbe</t>
+  </si>
+  <si>
+    <t>Ramiro O Vallejo</t>
+  </si>
+  <si>
+    <t>Ramiro A Vallejo</t>
+  </si>
+  <si>
+    <t>Roberto Peñafiel</t>
+  </si>
+  <si>
+    <t>Hernán Espinosa</t>
+  </si>
+  <si>
+    <t>J29QPX</t>
   </si>
 </sst>
 </file>
@@ -459,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -468,6 +474,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -804,12 +813,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7136B2E9-7B51-874A-BFBE-4CAB6091C4C3}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -827,8 +837,8 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>119</v>
+      <c r="B2" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -838,7 +848,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -849,7 +859,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -860,7 +870,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -871,8 +881,8 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>92</v>
+      <c r="B6" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -882,8 +892,8 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>106</v>
+      <c r="B7" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
@@ -893,8 +903,8 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>121</v>
+      <c r="B8" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -904,8 +914,8 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>122</v>
+      <c r="B9" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -915,8 +925,8 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>93</v>
+      <c r="B10" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -926,8 +936,8 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>94</v>
+      <c r="B11" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
@@ -937,8 +947,8 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>95</v>
+      <c r="B12" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
@@ -948,8 +958,8 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>96</v>
+      <c r="B13" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -959,8 +969,8 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>97</v>
+      <c r="B14" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
@@ -970,8 +980,8 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>98</v>
+      <c r="B15" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -981,8 +991,8 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>99</v>
+      <c r="B16" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>17</v>
@@ -992,8 +1002,8 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>120</v>
+      <c r="B17" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
@@ -1003,8 +1013,8 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>100</v>
+      <c r="B18" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -1014,8 +1024,8 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>101</v>
+      <c r="B19" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>20</v>
@@ -1025,8 +1035,8 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>102</v>
+      <c r="B20" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -1036,8 +1046,8 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>103</v>
+      <c r="B21" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>22</v>
@@ -1047,8 +1057,8 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>104</v>
+      <c r="B22" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>23</v>
@@ -1058,8 +1068,8 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>105</v>
+      <c r="B23" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
@@ -1069,8 +1079,8 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>107</v>
+      <c r="B24" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -1080,8 +1090,8 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>108</v>
+      <c r="B25" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>26</v>
@@ -1091,8 +1101,8 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>109</v>
+      <c r="B26" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>27</v>
@@ -1102,8 +1112,8 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>110</v>
+      <c r="B27" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>28</v>
@@ -1113,8 +1123,8 @@
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>111</v>
+      <c r="B28" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>29</v>
@@ -1124,8 +1134,8 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>112</v>
+      <c r="B29" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>30</v>
@@ -1135,8 +1145,8 @@
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>113</v>
+      <c r="B30" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>31</v>
@@ -1146,8 +1156,8 @@
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>114</v>
+      <c r="B31" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>32</v>
@@ -1157,8 +1167,8 @@
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>115</v>
+      <c r="B32" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>33</v>
@@ -1168,8 +1178,8 @@
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>116</v>
+      <c r="B33" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
@@ -1179,8 +1189,8 @@
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>117</v>
+      <c r="B34" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>35</v>
@@ -1190,8 +1200,8 @@
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>118</v>
+      <c r="B35" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>36</v>
@@ -1201,8 +1211,8 @@
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>66</v>
+      <c r="B36" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
@@ -1212,8 +1222,8 @@
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>67</v>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>38</v>
@@ -1223,8 +1233,8 @@
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>68</v>
+      <c r="B38" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>39</v>
@@ -1234,8 +1244,8 @@
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>69</v>
+      <c r="B39" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>40</v>
@@ -1245,8 +1255,8 @@
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>70</v>
+      <c r="B40" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>41</v>
@@ -1256,8 +1266,8 @@
       <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>71</v>
+      <c r="B41" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>42</v>
@@ -1267,8 +1277,8 @@
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>72</v>
+      <c r="B42" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>43</v>
@@ -1278,8 +1288,8 @@
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>73</v>
+      <c r="B43" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>44</v>
@@ -1289,8 +1299,8 @@
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>74</v>
+      <c r="B44" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>45</v>
@@ -1300,8 +1310,8 @@
       <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>75</v>
+      <c r="B45" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>46</v>
@@ -1311,8 +1321,8 @@
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>76</v>
+      <c r="B46" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>47</v>
@@ -1322,8 +1332,8 @@
       <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>77</v>
+      <c r="B47" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>48</v>
@@ -1333,155 +1343,199 @@
       <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>78</v>
+      <c r="B48" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>79</v>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>80</v>
+      <c r="B50" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>81</v>
+      <c r="B51" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>82</v>
+      <c r="B52" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>83</v>
+      <c r="B53" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>84</v>
+      <c r="B54" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>85</v>
+      <c r="B55" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>86</v>
+      <c r="B56" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>87</v>
+      <c r="B57" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>88</v>
+      <c r="B58" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>89</v>
+      <c r="B59" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>90</v>
+      <c r="B60" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>91</v>
+      <c r="B61" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>62</v>
       </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D74" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B258C627-4CCE-BC4C-B8FF-1EB0AC41B76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA1D6E-2C38-9F45-B171-F183B2311D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="2560" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>J29QPX</t>
+  </si>
+  <si>
+    <t>8PV3KZ</t>
+  </si>
+  <si>
+    <t>Jeffry Trujillo</t>
   </si>
 </sst>
 </file>
@@ -476,8 +482,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,7 +843,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -848,7 +854,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -859,7 +865,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -870,7 +876,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -881,7 +887,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -892,7 +898,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -903,7 +909,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -914,7 +920,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -925,7 +931,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -936,7 +942,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -947,7 +953,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -958,7 +964,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -969,7 +975,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -980,7 +986,7 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -991,7 +997,7 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1002,7 +1008,7 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1013,7 +1019,7 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1024,7 +1030,7 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1035,7 +1041,7 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1046,7 +1052,7 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1057,7 +1063,7 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1068,7 +1074,7 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1079,7 +1085,7 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1090,7 +1096,7 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1101,7 +1107,7 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1112,7 +1118,7 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -1123,7 +1129,7 @@
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1134,7 +1140,7 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -1145,7 +1151,7 @@
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1156,7 +1162,7 @@
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -1167,7 +1173,7 @@
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -1178,7 +1184,7 @@
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -1189,7 +1195,7 @@
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -1200,7 +1206,7 @@
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -1211,7 +1217,7 @@
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -1222,7 +1228,7 @@
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -1233,7 +1239,7 @@
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -1244,7 +1250,7 @@
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -1255,7 +1261,7 @@
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -1266,7 +1272,7 @@
       <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -1277,7 +1283,7 @@
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -1288,7 +1294,7 @@
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -1299,7 +1305,7 @@
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1310,7 +1316,7 @@
       <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -1321,7 +1327,7 @@
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -1332,7 +1338,7 @@
       <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -1343,7 +1349,7 @@
       <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -1354,7 +1360,7 @@
       <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -1365,7 +1371,7 @@
       <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -1376,7 +1382,7 @@
       <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -1387,7 +1393,7 @@
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -1398,7 +1404,7 @@
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -1409,7 +1415,7 @@
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -1420,7 +1426,7 @@
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -1431,7 +1437,7 @@
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -1442,7 +1448,7 @@
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -1453,7 +1459,7 @@
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -1464,7 +1470,7 @@
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -1475,7 +1481,7 @@
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -1486,7 +1492,7 @@
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -1497,11 +1503,22 @@
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA1D6E-2C38-9F45-B171-F183B2311D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7061657-37CC-AC45-BF3D-98EA9B9FD8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="2560" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
+    <workbookView xWindow="4940" yWindow="2920" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>ID</t>
   </si>
@@ -275,12 +275,6 @@
     <t>Benja Mucarsel B</t>
   </si>
   <si>
-    <t>Oscar Arteaga</t>
-  </si>
-  <si>
-    <t>Sebastian Larco</t>
-  </si>
-  <si>
     <t>Hipa Vásquez</t>
   </si>
   <si>
@@ -347,9 +341,6 @@
     <t>Luis Moreno</t>
   </si>
   <si>
-    <t>Jose Viera</t>
-  </si>
-  <si>
     <t>Paco Ortiz</t>
   </si>
   <si>
@@ -362,9 +353,6 @@
     <t>Carlos Castro</t>
   </si>
   <si>
-    <t>Carlitos y Patty</t>
-  </si>
-  <si>
     <t>Doménica Larrea</t>
   </si>
   <si>
@@ -417,6 +405,36 @@
   </si>
   <si>
     <t>Jeffry Trujillo</t>
+  </si>
+  <si>
+    <t>Fabián Procel</t>
+  </si>
+  <si>
+    <t>UHOAFN</t>
+  </si>
+  <si>
+    <t>Jonathan Vásquez</t>
+  </si>
+  <si>
+    <t>G9DBE7</t>
+  </si>
+  <si>
+    <t>Carlos F Castro</t>
+  </si>
+  <si>
+    <t>Sebastián Larco</t>
+  </si>
+  <si>
+    <t>Óscar Arteaga</t>
+  </si>
+  <si>
+    <t>José Viera</t>
+  </si>
+  <si>
+    <t>Kevin Puga</t>
+  </si>
+  <si>
+    <t>DX9TWC</t>
   </si>
 </sst>
 </file>
@@ -844,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -899,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
@@ -910,7 +928,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -921,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -1009,7 +1027,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
@@ -1075,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
@@ -1086,7 +1104,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -1097,7 +1115,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>26</v>
@@ -1108,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>27</v>
@@ -1119,7 +1137,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>28</v>
@@ -1130,7 +1148,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>29</v>
@@ -1141,7 +1159,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>30</v>
@@ -1152,7 +1170,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>31</v>
@@ -1163,7 +1181,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>32</v>
@@ -1174,7 +1192,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>33</v>
@@ -1185,7 +1203,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
@@ -1196,7 +1214,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>35</v>
@@ -1207,7 +1225,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>36</v>
@@ -1218,7 +1236,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
@@ -1229,7 +1247,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>38</v>
@@ -1240,7 +1258,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>39</v>
@@ -1251,7 +1269,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>40</v>
@@ -1262,7 +1280,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>41</v>
@@ -1273,7 +1291,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>42</v>
@@ -1284,7 +1302,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>43</v>
@@ -1295,7 +1313,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>44</v>
@@ -1306,7 +1324,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>45</v>
@@ -1317,7 +1335,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>46</v>
@@ -1328,7 +1346,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>47</v>
@@ -1339,7 +1357,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>48</v>
@@ -1350,7 +1368,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>49</v>
@@ -1361,7 +1379,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>50</v>
@@ -1372,7 +1390,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>51</v>
@@ -1383,7 +1401,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>52</v>
@@ -1394,7 +1412,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>53</v>
@@ -1405,7 +1423,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>54</v>
@@ -1416,7 +1434,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>55</v>
@@ -1427,7 +1445,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>56</v>
@@ -1438,7 +1456,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>57</v>
@@ -1449,7 +1467,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>58</v>
@@ -1460,7 +1478,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>59</v>
@@ -1471,7 +1489,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>60</v>
@@ -1482,7 +1500,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>61</v>
@@ -1493,7 +1511,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>62</v>
@@ -1504,10 +1522,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1515,43 +1533,70 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D64" s="2"/>
-    </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D67" s="2"/>
     </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D74" s="2"/>
     </row>
   </sheetData>

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7061657-37CC-AC45-BF3D-98EA9B9FD8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13F5F92-0B25-6840-945F-A7CD8D013485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="2920" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
+    <workbookView xWindow="-28800" yWindow="2560" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -242,9 +242,6 @@
     <t>Gabriel Cepeda</t>
   </si>
   <si>
-    <t>André Cepeda</t>
-  </si>
-  <si>
     <t>Daniel Larco</t>
   </si>
   <si>
@@ -305,9 +302,6 @@
     <t>Irene Vásquez</t>
   </si>
   <si>
-    <t>Javier Gracia</t>
-  </si>
-  <si>
     <t>Pepe Vaca</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
     <t>Daniel Guevara</t>
   </si>
   <si>
-    <t xml:space="preserve">Christian  Guevara </t>
-  </si>
-  <si>
     <t>Sergio Montalvo</t>
   </si>
   <si>
@@ -425,9 +416,6 @@
     <t>Sebastián Larco</t>
   </si>
   <si>
-    <t>Óscar Arteaga</t>
-  </si>
-  <si>
     <t>José Viera</t>
   </si>
   <si>
@@ -435,6 +423,18 @@
   </si>
   <si>
     <t>DX9TWC</t>
+  </si>
+  <si>
+    <t>André Encalada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Guevara </t>
+  </si>
+  <si>
+    <t>Javier García</t>
+  </si>
+  <si>
+    <t>Oscar Arteaga</t>
   </si>
 </sst>
 </file>
@@ -862,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -917,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
@@ -928,7 +928,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -961,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
@@ -983,7 +983,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -994,7 +994,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
@@ -1005,7 +1005,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -1016,7 +1016,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>17</v>
@@ -1027,7 +1027,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
@@ -1038,7 +1038,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -1049,7 +1049,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>20</v>
@@ -1060,7 +1060,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -1071,7 +1071,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>22</v>
@@ -1082,7 +1082,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>23</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
@@ -1104,7 +1104,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -1115,7 +1115,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>26</v>
@@ -1126,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>27</v>
@@ -1137,7 +1137,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>28</v>
@@ -1148,7 +1148,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>29</v>
@@ -1159,7 +1159,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>30</v>
@@ -1170,7 +1170,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>31</v>
@@ -1181,7 +1181,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>32</v>
@@ -1192,7 +1192,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>33</v>
@@ -1203,7 +1203,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
@@ -1214,7 +1214,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>35</v>
@@ -1225,7 +1225,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>36</v>
@@ -1236,7 +1236,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
@@ -1247,7 +1247,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>38</v>
@@ -1258,7 +1258,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>39</v>
@@ -1269,7 +1269,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>40</v>
@@ -1280,7 +1280,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>41</v>
@@ -1291,7 +1291,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>42</v>
@@ -1302,7 +1302,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>43</v>
@@ -1313,7 +1313,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>44</v>
@@ -1324,7 +1324,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>45</v>
@@ -1335,7 +1335,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>46</v>
@@ -1346,7 +1346,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>47</v>
@@ -1357,7 +1357,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>48</v>
@@ -1368,7 +1368,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>49</v>
@@ -1379,7 +1379,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>50</v>
@@ -1390,7 +1390,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>51</v>
@@ -1401,7 +1401,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>52</v>
@@ -1412,7 +1412,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>53</v>
@@ -1423,7 +1423,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>54</v>
@@ -1434,7 +1434,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>55</v>
@@ -1445,7 +1445,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>56</v>
@@ -1456,7 +1456,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>57</v>
@@ -1467,7 +1467,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>58</v>
@@ -1478,7 +1478,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>59</v>
@@ -1489,7 +1489,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>60</v>
@@ -1500,7 +1500,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>61</v>
@@ -1511,7 +1511,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>62</v>
@@ -1522,10 +1522,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -1544,10 +1544,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -1556,10 +1556,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1568,10 +1568,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D66" s="2"/>
     </row>

--- a/BD participantes.xlsx
+++ b/BD participantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upmsj/Desktop/UPMSJ /JF/polla/app/pm_project jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13F5F92-0B25-6840-945F-A7CD8D013485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3878CD40-6F92-FB41-91C2-A5E5E94C3D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="2560" windowWidth="28800" windowHeight="17400" xr2:uid="{FA559016-7FAB-0B47-8ABB-CBD3A3CB183F}"/>
   </bookViews>
@@ -386,9 +386,6 @@
     <t>Roberto Peñafiel</t>
   </si>
   <si>
-    <t>Hernán Espinosa</t>
-  </si>
-  <si>
     <t>J29QPX</t>
   </si>
   <si>
@@ -435,6 +432,9 @@
   </si>
   <si>
     <t>Oscar Arteaga</t>
+  </si>
+  <si>
+    <t>Hernán Espinoza</t>
   </si>
 </sst>
 </file>
@@ -917,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -961,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
@@ -1214,7 +1214,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>35</v>
@@ -1302,7 +1302,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>43</v>
@@ -1434,7 +1434,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>55</v>
@@ -1522,10 +1522,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -1544,10 +1544,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -1556,10 +1556,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1568,10 +1568,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="D66" s="2"/>
     </row>
